--- a/class_excel/data-files-optimization.xlsx
+++ b/class_excel/data-files-optimization.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nuna\Documents\GitHub\DADS7102\class_excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T00229\Documents\GitHub\DADS7102\class_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F8D3BDE-663E-4E30-9B46-A5FF7B530282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE3A7086-02D1-4CB9-8E6C-A4A9FB61FF00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="954" firstSheet="4" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="954" firstSheet="4" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sensitivity Report 1" sheetId="34" r:id="rId1"/>
@@ -83,7 +83,7 @@
     <definedName name="solver_adj" localSheetId="28" hidden="1">EOQ!$G$9:$I$9</definedName>
     <definedName name="solver_adj" localSheetId="20" hidden="1">FixedCost!$B$14:$F$15</definedName>
     <definedName name="solver_adj" localSheetId="21" hidden="1">Hub!$B$21:$M$21</definedName>
-    <definedName name="solver_adj" localSheetId="16" hidden="1">'HW3'!$E$6:$E$15</definedName>
+    <definedName name="solver_adj" localSheetId="16" hidden="1">'HW3'!$E$5:$E$14</definedName>
     <definedName name="solver_adj" localSheetId="5" hidden="1">LM_2!$B$10:$I$10</definedName>
     <definedName name="solver_adj" localSheetId="14" hidden="1">MCNF!$D$8:$D$13</definedName>
     <definedName name="solver_adj" localSheetId="7" hidden="1">ProdPlanning!$B$12:$G$12</definedName>
@@ -187,7 +187,7 @@
     <definedName name="solver_lhs1" localSheetId="28" hidden="1">EOQ!$J$15</definedName>
     <definedName name="solver_lhs1" localSheetId="20" hidden="1">FixedCost!$B$14:$F$14</definedName>
     <definedName name="solver_lhs1" localSheetId="21" hidden="1">Hub!$B$21:$M$21</definedName>
-    <definedName name="solver_lhs1" localSheetId="16" hidden="1">'HW3'!$E$6:$E$7</definedName>
+    <definedName name="solver_lhs1" localSheetId="16" hidden="1">'HW3'!$L$14:$L$17</definedName>
     <definedName name="solver_lhs1" localSheetId="5" hidden="1">LM_2!$J$12:$J$14</definedName>
     <definedName name="solver_lhs1" localSheetId="14" hidden="1">MCNF!$D$8:$D$13</definedName>
     <definedName name="solver_lhs1" localSheetId="7" hidden="1">ProdPlanning!$B$12:$G$12</definedName>
@@ -212,7 +212,7 @@
     <definedName name="solver_lhs2" localSheetId="19" hidden="1">CapitalBudget!$B$10:$H$10</definedName>
     <definedName name="solver_lhs2" localSheetId="20" hidden="1">FixedCost!$B$15:$F$15</definedName>
     <definedName name="solver_lhs2" localSheetId="21" hidden="1">Hub!$B$25:$B$36</definedName>
-    <definedName name="solver_lhs2" localSheetId="16" hidden="1">'HW3'!$L$10:$L$11</definedName>
+    <definedName name="solver_lhs2" localSheetId="16" hidden="1">'HW3'!$L$5</definedName>
     <definedName name="solver_lhs2" localSheetId="5" hidden="1">LM_2!$J$15</definedName>
     <definedName name="solver_lhs2" localSheetId="14" hidden="1">MCNF!$L$9:$L$13</definedName>
     <definedName name="solver_lhs2" localSheetId="7" hidden="1">ProdPlanning!$B$20:$G$20</definedName>
@@ -228,7 +228,7 @@
     <definedName name="solver_lhs22" localSheetId="8" hidden="1">project!$I$11</definedName>
     <definedName name="solver_lhs3" localSheetId="19" hidden="1">CapitalBudget!$C$15</definedName>
     <definedName name="solver_lhs3" localSheetId="20" hidden="1">FixedCost!$B$23:$B$24</definedName>
-    <definedName name="solver_lhs3" localSheetId="16" hidden="1">'HW3'!$L$15:$L$18</definedName>
+    <definedName name="solver_lhs3" localSheetId="16" hidden="1">'HW3'!$E$5:$E$6</definedName>
     <definedName name="solver_lhs3" localSheetId="5" hidden="1">LM_2!$J$15</definedName>
     <definedName name="solver_lhs3" localSheetId="14" hidden="1">MCNF!$L$20:$L$21</definedName>
     <definedName name="solver_lhs3" localSheetId="7" hidden="1">ProdPlanning!$B$20:$G$20</definedName>
@@ -238,7 +238,7 @@
     <definedName name="solver_lhs3" localSheetId="8" hidden="1">project!$I$22</definedName>
     <definedName name="solver_lhs3" localSheetId="15" hidden="1">RedBrandLogistics!$K$20:$K$21</definedName>
     <definedName name="solver_lhs4" localSheetId="19" hidden="1">CapitalBudget!$B$10:$H$10</definedName>
-    <definedName name="solver_lhs4" localSheetId="16" hidden="1">'HW3'!$L$6</definedName>
+    <definedName name="solver_lhs4" localSheetId="16" hidden="1">'HW3'!$L$9:$L$10</definedName>
     <definedName name="solver_lhs4" localSheetId="14" hidden="1">MCNF!$L$9:$L$11</definedName>
     <definedName name="solver_lhs4" localSheetId="8" hidden="1">project!$I$22</definedName>
     <definedName name="solver_lhs4" localSheetId="15" hidden="1">RedBrandLogistics!$K$9:$K$11</definedName>
@@ -394,7 +394,7 @@
     <definedName name="solver_opt" localSheetId="28" hidden="1">EOQ!$J$13</definedName>
     <definedName name="solver_opt" localSheetId="20" hidden="1">FixedCost!$B$30</definedName>
     <definedName name="solver_opt" localSheetId="21" hidden="1">Hub!$B$39</definedName>
-    <definedName name="solver_opt" localSheetId="16" hidden="1">'HW3'!$B$18</definedName>
+    <definedName name="solver_opt" localSheetId="16" hidden="1">'HW3'!$B$17</definedName>
     <definedName name="solver_opt" localSheetId="5" hidden="1">LM_2!$K$11</definedName>
     <definedName name="solver_opt" localSheetId="14" hidden="1">MCNF!$B$17</definedName>
     <definedName name="solver_opt" localSheetId="7" hidden="1">ProdPlanning!$H$28</definedName>
@@ -446,7 +446,7 @@
     <definedName name="solver_rel1" localSheetId="28" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="20" hidden="1">5</definedName>
     <definedName name="solver_rel1" localSheetId="21" hidden="1">5</definedName>
-    <definedName name="solver_rel1" localSheetId="16" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="16" hidden="1">3</definedName>
     <definedName name="solver_rel1" localSheetId="5" hidden="1">2</definedName>
     <definedName name="solver_rel1" localSheetId="14" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="7" hidden="1">1</definedName>
@@ -487,7 +487,7 @@
     <definedName name="solver_rel22" localSheetId="8" hidden="1">3</definedName>
     <definedName name="solver_rel3" localSheetId="19" hidden="1">1</definedName>
     <definedName name="solver_rel3" localSheetId="20" hidden="1">1</definedName>
-    <definedName name="solver_rel3" localSheetId="16" hidden="1">3</definedName>
+    <definedName name="solver_rel3" localSheetId="16" hidden="1">1</definedName>
     <definedName name="solver_rel3" localSheetId="5" hidden="1">1</definedName>
     <definedName name="solver_rel3" localSheetId="14" hidden="1">3</definedName>
     <definedName name="solver_rel3" localSheetId="7" hidden="1">3</definedName>
@@ -513,7 +513,7 @@
     <definedName name="solver_rhs1" localSheetId="28" hidden="1">EOQ!$L$15</definedName>
     <definedName name="solver_rhs1" localSheetId="20" hidden="1">"binary"</definedName>
     <definedName name="solver_rhs1" localSheetId="21" hidden="1">binary</definedName>
-    <definedName name="solver_rhs1" localSheetId="16" hidden="1">'HW3'!$G$6:$G$7</definedName>
+    <definedName name="solver_rhs1" localSheetId="16" hidden="1">'HW3'!$N$14:$N$17</definedName>
     <definedName name="solver_rhs1" localSheetId="5" hidden="1">LM_2!$L$12:$L$14</definedName>
     <definedName name="solver_rhs1" localSheetId="14" hidden="1">MCNF!$F$8:$F$13</definedName>
     <definedName name="solver_rhs1" localSheetId="7" hidden="1">ProdPlanning!$B$14:$G$14</definedName>
@@ -538,7 +538,7 @@
     <definedName name="solver_rhs2" localSheetId="19" hidden="1">"binary"</definedName>
     <definedName name="solver_rhs2" localSheetId="20" hidden="1">FixedCost!$B$17:$F$17</definedName>
     <definedName name="solver_rhs2" localSheetId="21" hidden="1">Hub!$D$25:$D$36</definedName>
-    <definedName name="solver_rhs2" localSheetId="16" hidden="1">'HW3'!$N$10:$N$11</definedName>
+    <definedName name="solver_rhs2" localSheetId="16" hidden="1">'HW3'!$N$5</definedName>
     <definedName name="solver_rhs2" localSheetId="5" hidden="1">LM_2!$L$15</definedName>
     <definedName name="solver_rhs2" localSheetId="14" hidden="1">MCNF!$N$9:$N$13</definedName>
     <definedName name="solver_rhs2" localSheetId="7" hidden="1">ProdPlanning!$B$22:$G$22</definedName>
@@ -554,7 +554,7 @@
     <definedName name="solver_rhs22" localSheetId="8" hidden="1">EFinish</definedName>
     <definedName name="solver_rhs3" localSheetId="19" hidden="1">0</definedName>
     <definedName name="solver_rhs3" localSheetId="20" hidden="1">FixedCost!$D$23:$D$24</definedName>
-    <definedName name="solver_rhs3" localSheetId="16" hidden="1">'HW3'!$N$15:$N$18</definedName>
+    <definedName name="solver_rhs3" localSheetId="16" hidden="1">'HW3'!$G$5:$G$6</definedName>
     <definedName name="solver_rhs3" localSheetId="5" hidden="1">LM_2!$L$15</definedName>
     <definedName name="solver_rhs3" localSheetId="14" hidden="1">MCNF!$N$20:$N$21</definedName>
     <definedName name="solver_rhs3" localSheetId="7" hidden="1">0</definedName>
@@ -564,7 +564,7 @@
     <definedName name="solver_rhs3" localSheetId="8" hidden="1">NFinish</definedName>
     <definedName name="solver_rhs3" localSheetId="15" hidden="1">RedBrandLogistics!$M$20:$M$21</definedName>
     <definedName name="solver_rhs4" localSheetId="19" hidden="1">1</definedName>
-    <definedName name="solver_rhs4" localSheetId="16" hidden="1">'HW3'!$N$6</definedName>
+    <definedName name="solver_rhs4" localSheetId="16" hidden="1">'HW3'!$N$9:$N$10</definedName>
     <definedName name="solver_rhs4" localSheetId="14" hidden="1">MCNF!$N$9:$N$11</definedName>
     <definedName name="solver_rhs4" localSheetId="8" hidden="1">project!$K$22</definedName>
     <definedName name="solver_rhs4" localSheetId="15" hidden="1">RedBrandLogistics!$M$9:$M$11</definedName>
@@ -760,6 +760,9 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -855,7 +858,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="593">
   <si>
     <t>Assembling and testing computers</t>
   </si>
@@ -2911,6 +2914,9 @@
   <si>
     <t xml:space="preserve">customer constraint </t>
   </si>
+  <si>
+    <t>[GhianiLaportMusmanno p.334]</t>
+  </si>
 </sst>
 </file>
 
@@ -2932,9 +2938,9 @@
     <numFmt numFmtId="170" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="171" formatCode="&quot;$&quot;#,##0.00;\-&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="172" formatCode="&quot;฿&quot;#,##0.00"/>
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="173" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3127,6 +3133,15 @@
       <b/>
       <sz val="11"/>
       <color indexed="18"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3429,7 +3444,7 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3602,20 +3617,41 @@
     <xf numFmtId="172" fontId="4" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1"/>
     <xf numFmtId="43" fontId="4" fillId="8" borderId="11" xfId="6" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
+    </xf>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="0" fillId="6" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="2"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -4901,9 +4937,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4941,9 +4977,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4976,9 +5012,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -5011,9 +5064,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -9394,7 +9464,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="11">
-        <f t="shared" ref="K10:K13" si="3">SUMIF($B$8:$B$13, I13,$D$8:$D$13)</f>
+        <f t="shared" ref="K13" si="3">SUMIF($B$8:$B$13, I13,$D$8:$D$13)</f>
         <v>90</v>
       </c>
       <c r="L13" s="11">
@@ -10615,7 +10685,7 @@
         <v>300</v>
       </c>
       <c r="J10" s="11">
-        <f t="shared" ref="J10:J11" si="2">SUMIF($B$8:$B$33,H10,$D$8:$D$33)</f>
+        <f t="shared" ref="J10" si="2">SUMIF($B$8:$B$33,H10,$D$8:$D$33)</f>
         <v>0</v>
       </c>
       <c r="K10" s="11">
@@ -11219,423 +11289,577 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{416C8E38-3B77-4A74-A10C-2B5B49E38902}">
-  <dimension ref="A4:N18"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
     <col min="11" max="11" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:14">
-      <c r="A4" s="1" t="s">
+    <row r="1" spans="1:15" ht="15.75">
+      <c r="A1" s="120" t="s">
+        <v>592</v>
+      </c>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="122"/>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="123"/>
+      <c r="B2" s="108"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
+      <c r="F2" s="108"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="108"/>
+      <c r="I2" s="108"/>
+      <c r="J2" s="108"/>
+      <c r="K2" s="108"/>
+      <c r="L2" s="108"/>
+      <c r="M2" s="108"/>
+      <c r="N2" s="108"/>
+      <c r="O2" s="124"/>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="125" t="s">
         <v>583</v>
       </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1" t="s">
+      <c r="B3" s="108"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="108"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="B5" t="s">
+      <c r="J3" s="108"/>
+      <c r="K3" s="108"/>
+      <c r="L3" s="108"/>
+      <c r="M3" s="108"/>
+      <c r="N3" s="108"/>
+      <c r="O3" s="124"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="123"/>
+      <c r="B4" s="108" t="s">
         <v>581</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C4" s="108" t="s">
         <v>223</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D4" s="108" t="s">
         <v>582</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E4" s="108" t="s">
         <v>225</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="F4" s="108"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="110" t="s">
         <v>588</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J4" s="110" t="s">
         <v>231</v>
       </c>
-      <c r="K5" s="111" t="s">
+      <c r="K4" s="111" t="s">
         <v>232</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L4" s="108" t="s">
         <v>589</v>
       </c>
-      <c r="N5" t="s">
+      <c r="M4" s="108"/>
+      <c r="N4" s="108" t="s">
         <v>590</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
+      <c r="O4" s="124"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="123"/>
+      <c r="B5" s="108">
+        <v>1</v>
+      </c>
+      <c r="C5" s="108">
         <v>2</v>
       </c>
+      <c r="D5" s="112">
+        <v>24.5</v>
+      </c>
+      <c r="E5" s="113">
+        <v>150000</v>
+      </c>
+      <c r="F5" s="130" t="s">
+        <v>278</v>
+      </c>
+      <c r="G5" s="129">
+        <v>150000</v>
+      </c>
+      <c r="H5" s="108"/>
+      <c r="I5" s="110">
+        <v>1</v>
+      </c>
+      <c r="J5" s="110">
+        <f>SUMIF($B$5:$B$14,$I5,$E$5:$E$14)</f>
+        <v>290000</v>
+      </c>
+      <c r="K5" s="110">
+        <f>SUMIF($C$5:$C$14,$I5,$E$5:$E$14)</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="108">
+        <f>J5-K5</f>
+        <v>290000</v>
+      </c>
+      <c r="M5" s="110" t="s">
+        <v>354</v>
+      </c>
+      <c r="N5" s="115">
+        <v>290000</v>
+      </c>
+      <c r="O5" s="124"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="123"/>
+      <c r="B6" s="108">
+        <v>1</v>
+      </c>
+      <c r="C6" s="108">
+        <v>3</v>
+      </c>
       <c r="D6" s="112">
-        <v>24.5</v>
-      </c>
-      <c r="E6" s="53">
+        <v>26</v>
+      </c>
+      <c r="E6" s="113">
+        <v>140000</v>
+      </c>
+      <c r="F6" s="130" t="s">
+        <v>278</v>
+      </c>
+      <c r="G6" s="129">
         <v>150000</v>
       </c>
-      <c r="F6" s="28" t="s">
-        <v>278</v>
-      </c>
-      <c r="G6" s="113">
+      <c r="H6" s="108"/>
+      <c r="I6" s="109"/>
+      <c r="J6" s="110"/>
+      <c r="K6" s="116"/>
+      <c r="L6" s="108"/>
+      <c r="M6" s="108"/>
+      <c r="N6" s="108"/>
+      <c r="O6" s="124"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="123"/>
+      <c r="B7" s="108">
+        <v>2</v>
+      </c>
+      <c r="C7" s="108">
+        <v>4</v>
+      </c>
+      <c r="D7" s="112">
+        <v>9.6</v>
+      </c>
+      <c r="E7" s="113">
+        <v>90000</v>
+      </c>
+      <c r="F7" s="114"/>
+      <c r="G7" s="108"/>
+      <c r="H7" s="109"/>
+      <c r="I7" s="109" t="s">
+        <v>587</v>
+      </c>
+      <c r="J7" s="110"/>
+      <c r="K7" s="116"/>
+      <c r="L7" s="108"/>
+      <c r="M7" s="108"/>
+      <c r="N7" s="108"/>
+      <c r="O7" s="124"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="123"/>
+      <c r="B8" s="108">
+        <v>2</v>
+      </c>
+      <c r="C8" s="108">
+        <v>5</v>
+      </c>
+      <c r="D8" s="112">
+        <v>7</v>
+      </c>
+      <c r="E8" s="113">
+        <v>60000</v>
+      </c>
+      <c r="F8" s="114"/>
+      <c r="G8" s="108"/>
+      <c r="H8" s="108"/>
+      <c r="I8" s="110" t="s">
+        <v>588</v>
+      </c>
+      <c r="J8" s="110" t="s">
+        <v>231</v>
+      </c>
+      <c r="K8" s="111" t="s">
+        <v>232</v>
+      </c>
+      <c r="L8" s="108" t="s">
+        <v>589</v>
+      </c>
+      <c r="M8" s="108"/>
+      <c r="N8" s="108" t="s">
+        <v>590</v>
+      </c>
+      <c r="O8" s="124"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="123"/>
+      <c r="B9" s="108">
+        <v>2</v>
+      </c>
+      <c r="C9" s="108">
+        <v>6</v>
+      </c>
+      <c r="D9" s="112">
+        <v>15.2</v>
+      </c>
+      <c r="E9" s="113">
+        <v>0</v>
+      </c>
+      <c r="F9" s="114"/>
+      <c r="G9" s="108"/>
+      <c r="H9" s="108"/>
+      <c r="I9" s="108">
+        <v>2</v>
+      </c>
+      <c r="J9" s="110">
+        <f>SUMIF($B$5:$B$14,$I9,$E$5:$E$14)</f>
         <v>150000</v>
       </c>
-      <c r="I6" s="2">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2">
-        <f>SUMIF($B$6:$B$15,$I6,$E$6:$E$15)</f>
-        <v>290000</v>
-      </c>
-      <c r="K6" s="2">
-        <f>SUMIF($C$6:$C$15,$I6,$E$6:$E$15)</f>
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <f>J6-K6</f>
-        <v>290000</v>
-      </c>
-      <c r="M6" s="2" t="s">
+      <c r="K9" s="110">
+        <f>SUMIF($C$5:$C$14,$I9,$E$5:$E$14)</f>
+        <v>150000</v>
+      </c>
+      <c r="L9" s="108">
+        <f>J9-K9</f>
+        <v>0</v>
+      </c>
+      <c r="M9" s="110" t="s">
         <v>354</v>
       </c>
-      <c r="N6" s="76">
-        <v>290000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
+      <c r="N9" s="115">
+        <v>0</v>
+      </c>
+      <c r="O9" s="124"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="123"/>
+      <c r="B10" s="108">
+        <v>2</v>
+      </c>
+      <c r="C10" s="108">
+        <v>7</v>
+      </c>
+      <c r="D10" s="112">
+        <v>28.5</v>
+      </c>
+      <c r="E10" s="113">
+        <v>0</v>
+      </c>
+      <c r="F10" s="114"/>
+      <c r="G10" s="108"/>
+      <c r="H10" s="108"/>
+      <c r="I10" s="108">
         <v>3</v>
       </c>
-      <c r="D7" s="112">
-        <v>26</v>
-      </c>
-      <c r="E7" s="53">
+      <c r="J10" s="110">
+        <f>SUMIF($B$5:$B$14,$I10,$E$5:$E$14)</f>
         <v>140000</v>
       </c>
-      <c r="F7" s="28" t="s">
-        <v>278</v>
-      </c>
-      <c r="G7" s="113">
-        <v>150000</v>
-      </c>
-      <c r="I7" s="1"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="109"/>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="B8">
-        <v>2</v>
-      </c>
-      <c r="C8">
+      <c r="K10" s="110">
+        <f>SUMIF($C$5:$C$14,$I10,$E$5:$E$14)</f>
+        <v>140000</v>
+      </c>
+      <c r="L10" s="108">
+        <f>J10-K10</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="110" t="s">
+        <v>354</v>
+      </c>
+      <c r="N10" s="115">
+        <v>0</v>
+      </c>
+      <c r="O10" s="124"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="123"/>
+      <c r="B11" s="108">
+        <v>3</v>
+      </c>
+      <c r="C11" s="108">
         <v>4</v>
       </c>
-      <c r="D8" s="112">
-        <v>9.6</v>
-      </c>
-      <c r="E8" s="53">
+      <c r="D11" s="112">
+        <v>19.5</v>
+      </c>
+      <c r="E11" s="113">
+        <v>0</v>
+      </c>
+      <c r="F11" s="114"/>
+      <c r="G11" s="108"/>
+      <c r="H11" s="108"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="110"/>
+      <c r="K11" s="117"/>
+      <c r="L11" s="108"/>
+      <c r="M11" s="108"/>
+      <c r="N11" s="108"/>
+      <c r="O11" s="124"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="123"/>
+      <c r="B12" s="108">
+        <v>3</v>
+      </c>
+      <c r="C12" s="108">
+        <v>5</v>
+      </c>
+      <c r="D12" s="112">
+        <v>13.3</v>
+      </c>
+      <c r="E12" s="113">
+        <v>20000</v>
+      </c>
+      <c r="F12" s="114"/>
+      <c r="G12" s="108"/>
+      <c r="H12" s="108"/>
+      <c r="I12" s="109" t="s">
+        <v>591</v>
+      </c>
+      <c r="J12" s="108"/>
+      <c r="K12" s="108"/>
+      <c r="L12" s="108"/>
+      <c r="M12" s="108"/>
+      <c r="N12" s="108"/>
+      <c r="O12" s="124"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="123"/>
+      <c r="B13" s="108">
+        <v>3</v>
+      </c>
+      <c r="C13" s="108">
+        <v>6</v>
+      </c>
+      <c r="D13" s="112">
+        <v>5</v>
+      </c>
+      <c r="E13" s="113">
+        <v>50000</v>
+      </c>
+      <c r="F13" s="114"/>
+      <c r="G13" s="108"/>
+      <c r="H13" s="108"/>
+      <c r="I13" s="110" t="s">
+        <v>588</v>
+      </c>
+      <c r="J13" s="110" t="s">
+        <v>231</v>
+      </c>
+      <c r="K13" s="111" t="s">
+        <v>232</v>
+      </c>
+      <c r="L13" s="108" t="s">
+        <v>589</v>
+      </c>
+      <c r="M13" s="108"/>
+      <c r="N13" s="108" t="s">
+        <v>590</v>
+      </c>
+      <c r="O13" s="124"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="123"/>
+      <c r="B14" s="108">
+        <v>3</v>
+      </c>
+      <c r="C14" s="108">
+        <v>7</v>
+      </c>
+      <c r="D14" s="112">
+        <v>11.3</v>
+      </c>
+      <c r="E14" s="113">
+        <v>70000</v>
+      </c>
+      <c r="F14" s="114"/>
+      <c r="G14" s="108"/>
+      <c r="H14" s="108"/>
+      <c r="I14" s="108">
+        <v>4</v>
+      </c>
+      <c r="J14" s="110">
+        <f>SUMIF($B$5:$B$14,$I14,$E$5:$E$14)</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="110">
+        <f>SUMIF($C$5:$C$14,$I14,$E$5:$E$14)</f>
         <v>90000</v>
       </c>
-      <c r="F8" s="28"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="J8" s="2"/>
-      <c r="K8" s="109"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
+      <c r="L14" s="108">
+        <f>J14-K14</f>
+        <v>-90000</v>
+      </c>
+      <c r="M14" s="110" t="s">
+        <v>220</v>
+      </c>
+      <c r="N14" s="118">
+        <v>-90000</v>
+      </c>
+      <c r="O14" s="124"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="123"/>
+      <c r="B15" s="108"/>
+      <c r="C15" s="108"/>
+      <c r="D15" s="108"/>
+      <c r="E15" s="108"/>
+      <c r="F15" s="108"/>
+      <c r="G15" s="108"/>
+      <c r="H15" s="108"/>
+      <c r="I15" s="108">
         <v>5</v>
       </c>
-      <c r="D9" s="112">
-        <v>7</v>
-      </c>
-      <c r="E9" s="53">
-        <v>60000</v>
-      </c>
-      <c r="F9" s="28"/>
-      <c r="I9" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="K9" s="111" t="s">
-        <v>232</v>
-      </c>
-      <c r="L9" t="s">
-        <v>589</v>
-      </c>
-      <c r="N9" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="B10">
-        <v>2</v>
-      </c>
-      <c r="C10">
+      <c r="J15" s="110">
+        <f t="shared" ref="J15:J17" si="0">SUMIF($B$5:$B$14,$I15,$E$5:$E$14)</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="110">
+        <f t="shared" ref="K15:K16" si="1">SUMIF($C$5:$C$14,$I15,$E$5:$E$14)</f>
+        <v>80000</v>
+      </c>
+      <c r="L15" s="108">
+        <f t="shared" ref="L15:L17" si="2">J15-K15</f>
+        <v>-80000</v>
+      </c>
+      <c r="M15" s="110" t="s">
+        <v>220</v>
+      </c>
+      <c r="N15" s="118">
+        <v>-80000</v>
+      </c>
+      <c r="O15" s="124"/>
+    </row>
+    <row r="16" spans="1:15" ht="14.25" customHeight="1">
+      <c r="A16" s="125" t="s">
+        <v>584</v>
+      </c>
+      <c r="B16" s="108"/>
+      <c r="C16" s="108"/>
+      <c r="D16" s="108"/>
+      <c r="E16" s="108"/>
+      <c r="F16" s="108"/>
+      <c r="G16" s="108"/>
+      <c r="H16" s="108"/>
+      <c r="I16" s="108">
         <v>6</v>
       </c>
-      <c r="D10" s="112">
-        <v>15.2</v>
-      </c>
-      <c r="E10" s="53">
-        <v>0</v>
-      </c>
-      <c r="F10" s="28"/>
-      <c r="I10">
-        <v>2</v>
-      </c>
-      <c r="J10" s="2">
-        <f>SUMIF($B$6:$B$15,$I10,$E$6:$E$15)</f>
-        <v>150000</v>
-      </c>
-      <c r="K10" s="2">
-        <f>SUMIF($C$6:$C$15,$I10,$E$6:$E$15)</f>
-        <v>150000</v>
-      </c>
-      <c r="L10">
-        <f>J10-K10</f>
-        <v>0</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="N10" s="76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="B11">
-        <v>2</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-      <c r="D11" s="112">
-        <v>28.5</v>
-      </c>
-      <c r="E11" s="53">
-        <v>0</v>
-      </c>
-      <c r="F11" s="28"/>
-      <c r="I11">
-        <v>3</v>
-      </c>
-      <c r="J11" s="2">
-        <f>SUMIF($B$6:$B$15,$I11,$E$6:$E$15)</f>
-        <v>140000</v>
-      </c>
-      <c r="K11" s="2">
-        <f>SUMIF($C$6:$C$15,$I11,$E$6:$E$15)</f>
-        <v>140000</v>
-      </c>
-      <c r="L11">
-        <f>J11-K11</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="N11" s="76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="B12">
-        <v>3</v>
-      </c>
-      <c r="C12">
-        <v>4</v>
-      </c>
-      <c r="D12" s="112">
-        <v>19.5</v>
-      </c>
-      <c r="E12" s="53">
-        <v>0</v>
-      </c>
-      <c r="F12" s="28"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="110"/>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="B13">
-        <v>3</v>
-      </c>
-      <c r="C13">
-        <v>5</v>
-      </c>
-      <c r="D13" s="112">
-        <v>13.3</v>
-      </c>
-      <c r="E13" s="53">
-        <v>20000</v>
-      </c>
-      <c r="F13" s="28"/>
-      <c r="I13" s="1" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="B14">
-        <v>3</v>
-      </c>
-      <c r="C14">
-        <v>6</v>
-      </c>
-      <c r="D14" s="112">
-        <v>5</v>
-      </c>
-      <c r="E14" s="53">
-        <v>50000</v>
-      </c>
-      <c r="F14" s="28"/>
-      <c r="I14" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="K14" s="111" t="s">
-        <v>232</v>
-      </c>
-      <c r="L14" t="s">
-        <v>589</v>
-      </c>
-      <c r="N14" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="B15">
-        <v>3</v>
-      </c>
-      <c r="C15">
-        <v>7</v>
-      </c>
-      <c r="D15" s="112">
-        <v>11.3</v>
-      </c>
-      <c r="E15" s="53">
-        <v>70000</v>
-      </c>
-      <c r="F15" s="28"/>
-      <c r="I15">
-        <v>4</v>
-      </c>
-      <c r="J15" s="2">
-        <f>SUMIF($B$6:$B$15,$I15,$E$6:$E$15)</f>
-        <v>0</v>
-      </c>
-      <c r="K15" s="2">
-        <f>SUMIF($C$6:$C$15,$I15,$E$6:$E$15)</f>
-        <v>90000</v>
-      </c>
-      <c r="L15">
-        <f>J15-K15</f>
-        <v>-90000</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="N15" s="114">
-        <v>-90000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="I16">
-        <v>5</v>
-      </c>
-      <c r="J16" s="2">
-        <f t="shared" ref="J16:J18" si="0">SUMIF($B$6:$B$15,$I16,$E$6:$E$15)</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="2">
-        <f t="shared" ref="K16:K17" si="1">SUMIF($C$6:$C$15,$I16,$E$6:$E$15)</f>
-        <v>80000</v>
-      </c>
-      <c r="L16">
-        <f t="shared" ref="L16:L18" si="2">J16-K16</f>
-        <v>-80000</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="N16" s="114">
-        <v>-80000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A17" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="I17">
-        <v>6</v>
-      </c>
-      <c r="J17" s="2">
-        <f>SUMIF($B$6:$B$15,$I17,$E$6:$E$15)</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="2">
+      <c r="J16" s="110">
+        <f>SUMIF($B$5:$B$14,$I16,$E$5:$E$14)</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="110">
         <f t="shared" si="1"/>
         <v>50000</v>
       </c>
-      <c r="L17">
+      <c r="L16" s="108">
         <f t="shared" si="2"/>
         <v>-50000</v>
       </c>
-      <c r="M17" s="2" t="s">
+      <c r="M16" s="110" t="s">
         <v>220</v>
       </c>
-      <c r="N17" s="114">
+      <c r="N16" s="118">
         <v>-50000</v>
       </c>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" t="s">
+      <c r="O16" s="124"/>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="123" t="s">
         <v>585</v>
       </c>
-      <c r="B18" s="102">
-        <f>SUMPRODUCT(D6:D15,E6:E15)</f>
+      <c r="B17" s="128">
+        <f>SUMPRODUCT(D5:D14,E5:E14)</f>
         <v>9906000</v>
       </c>
-      <c r="I18">
+      <c r="C17" s="108"/>
+      <c r="D17" s="108"/>
+      <c r="E17" s="108"/>
+      <c r="F17" s="108"/>
+      <c r="G17" s="108"/>
+      <c r="H17" s="108"/>
+      <c r="I17" s="108">
         <v>7</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J17" s="110">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K18" s="2">
-        <f>SUMIF($C$6:$C$15,$I18,$E$6:$E$15)</f>
+      <c r="K17" s="110">
+        <f>SUMIF($C$5:$C$14,$I17,$E$5:$E$14)</f>
         <v>70000</v>
       </c>
-      <c r="L18">
+      <c r="L17" s="108">
         <f t="shared" si="2"/>
         <v>-70000</v>
       </c>
-      <c r="M18" s="2" t="s">
+      <c r="M17" s="110" t="s">
         <v>220</v>
       </c>
-      <c r="N18" s="114">
+      <c r="N17" s="118">
         <v>-70000</v>
+      </c>
+      <c r="O17" s="124"/>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" s="126"/>
+      <c r="B18" s="119"/>
+      <c r="C18" s="119"/>
+      <c r="D18" s="119"/>
+      <c r="E18" s="119"/>
+      <c r="F18" s="119"/>
+      <c r="G18" s="119"/>
+      <c r="H18" s="119"/>
+      <c r="I18" s="119"/>
+      <c r="J18" s="119"/>
+      <c r="K18" s="119"/>
+      <c r="L18" s="119"/>
+      <c r="M18" s="119"/>
+      <c r="N18" s="119"/>
+      <c r="O18" s="127"/>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="L21">
+        <v>9906000</v>
       </c>
     </row>
   </sheetData>
@@ -21015,13 +21239,13 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="108" t="s">
+      <c r="A7" s="131" t="s">
         <v>444</v>
       </c>
-      <c r="B7" s="108"/>
-      <c r="C7" s="108"/>
-      <c r="D7" s="108"/>
-      <c r="E7" s="108"/>
+      <c r="B7" s="131"/>
+      <c r="C7" s="131"/>
+      <c r="D7" s="131"/>
+      <c r="E7" s="131"/>
       <c r="F7" s="92">
         <f>SUMPRODUCT(F2:F5,E2:E5)</f>
         <v>5513.1568127458449</v>

--- a/class_excel/data-files-optimization.xlsx
+++ b/class_excel/data-files-optimization.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nuna\Documents\GitHub\DADS7102\class_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40374404-D9B9-44F6-8F4D-A22550AA3498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9271FA9A-A317-4300-BDD7-B0ACC9323073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="954" firstSheet="8" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="954" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sensitivity Report 1" sheetId="34" r:id="rId1"/>
@@ -25154,21 +25154,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005D21A9346877C94FBE0D2EF98A54C8DF" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="751dbf132c53fd3bc3488d6191458457">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="500c6692915ba10984c0aabd49f31b22">
     <xsd:element name="properties">
@@ -25282,10 +25267,32 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE94C634-99D9-44FC-B2A2-D1462FE9BD9E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{633191C1-D2B6-4B97-A701-AFB02492B9AF}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
@@ -25300,16 +25307,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{633191C1-D2B6-4B97-A701-AFB02492B9AF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE94C634-99D9-44FC-B2A2-D1462FE9BD9E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>

--- a/class_excel/data-files-optimization.xlsx
+++ b/class_excel/data-files-optimization.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\DADS7102\class_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E79F6DE-F2BA-4693-93EC-5BA8C90FCC27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ABC8A3D-02B7-4B08-9C6A-7829A61217AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="954" firstSheet="20" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="954" firstSheet="21" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sensitivity Report 1" sheetId="34" r:id="rId1"/>
@@ -41,12 +41,13 @@
     <sheet name="MMULT" sheetId="13" r:id="rId26"/>
     <sheet name="MDETERM" sheetId="21" r:id="rId27"/>
     <sheet name="Peakload" sheetId="15" r:id="rId28"/>
-    <sheet name="Portfolio" sheetId="14" r:id="rId29"/>
-    <sheet name="EOQ" sheetId="23" r:id="rId30"/>
-    <sheet name="SVM1" sheetId="24" r:id="rId31"/>
-    <sheet name="MLE" sheetId="25" r:id="rId32"/>
-    <sheet name="OLS" sheetId="30" r:id="rId33"/>
-    <sheet name="Location" sheetId="29" r:id="rId34"/>
+    <sheet name="GameTheory" sheetId="40" r:id="rId29"/>
+    <sheet name="Portfolio" sheetId="14" r:id="rId30"/>
+    <sheet name="EOQ" sheetId="23" r:id="rId31"/>
+    <sheet name="SVM1" sheetId="24" r:id="rId32"/>
+    <sheet name="MLE" sheetId="25" r:id="rId33"/>
+    <sheet name="OLS" sheetId="30" r:id="rId34"/>
+    <sheet name="Location" sheetId="29" r:id="rId35"/>
   </sheets>
   <definedNames>
     <definedName name="AFinish">project!$K$6</definedName>
@@ -81,12 +82,13 @@
     <definedName name="solver_adj" localSheetId="11" hidden="1">AssignmentProblem!$C$13:$F$16</definedName>
     <definedName name="solver_adj" localSheetId="20" hidden="1">CapitalBudget!$B$10:$H$10</definedName>
     <definedName name="solver_adj" localSheetId="6" hidden="1">Dual!$I$4:$L$4</definedName>
-    <definedName name="solver_adj" localSheetId="29" hidden="1">EOQ!$B$6</definedName>
+    <definedName name="solver_adj" localSheetId="30" hidden="1">EOQ!$B$6</definedName>
     <definedName name="solver_adj" localSheetId="21" hidden="1">FixedCost!$B$14:$F$15</definedName>
+    <definedName name="solver_adj" localSheetId="28" hidden="1">GameTheory!$B$2:$D$2</definedName>
     <definedName name="solver_adj" localSheetId="22" hidden="1">Hub!$B$21:$M$21</definedName>
     <definedName name="solver_adj" localSheetId="16" hidden="1">'HW3'!$E$5:$E$14</definedName>
     <definedName name="solver_adj" localSheetId="5" hidden="1">LM_2!$B$10:$I$10</definedName>
-    <definedName name="solver_adj" localSheetId="33" hidden="1">Location!$B$6:$C$6</definedName>
+    <definedName name="solver_adj" localSheetId="34" hidden="1">Location!$B$6:$C$6</definedName>
     <definedName name="solver_adj" localSheetId="14" hidden="1">MCNF!$D$8:$D$13</definedName>
     <definedName name="solver_adj" localSheetId="27" hidden="1">Peakload!$B$13:$C$13,Peakload!$B$15</definedName>
     <definedName name="solver_adj" localSheetId="7" hidden="1">ProdPlanning!$B$12:$G$12</definedName>
@@ -96,18 +98,19 @@
     <definedName name="solver_adj" localSheetId="8" hidden="1">project!$I$6:$J$19,project!$I$22</definedName>
     <definedName name="solver_adj" localSheetId="15" hidden="1">RedBrandLogistics!$D$8:$D$33</definedName>
     <definedName name="solver_adj" localSheetId="17" hidden="1">set_covering_model!$B$2:$G$2</definedName>
-    <definedName name="solver_adj" localSheetId="30" hidden="1">'SVM1'!$B$2:$D$2,'SVM1'!$F$2</definedName>
+    <definedName name="solver_adj" localSheetId="31" hidden="1">'SVM1'!$B$2:$D$2,'SVM1'!$F$2</definedName>
     <definedName name="solver_adj" localSheetId="10" hidden="1">Transport1!$C$13:$F$15</definedName>
     <definedName name="solver_adj" localSheetId="23" hidden="1">WorkerScheduling!$N$3:$T$3</definedName>
     <definedName name="solver_cvg" localSheetId="11" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="20" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="6" hidden="1">0.0001</definedName>
-    <definedName name="solver_cvg" localSheetId="29" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="30" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="21" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="28" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="22" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="16" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="5" hidden="1">0.0001</definedName>
-    <definedName name="solver_cvg" localSheetId="33" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="34" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="14" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="27" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="7" hidden="1">0.0001</definedName>
@@ -122,12 +125,13 @@
     <definedName name="solver_drv" localSheetId="11" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="20" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="6" hidden="1">1</definedName>
-    <definedName name="solver_drv" localSheetId="29" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="30" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="21" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="28" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="22" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="16" hidden="1">2</definedName>
     <definedName name="solver_drv" localSheetId="5" hidden="1">1</definedName>
-    <definedName name="solver_drv" localSheetId="33" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="34" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="14" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="27" hidden="1">2</definedName>
     <definedName name="solver_drv" localSheetId="7" hidden="1">1</definedName>
@@ -142,12 +146,13 @@
     <definedName name="solver_eng" localSheetId="11" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="20" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="6" hidden="1">2</definedName>
-    <definedName name="solver_eng" localSheetId="29" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="30" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="21" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="28" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="22" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="16" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="5" hidden="1">2</definedName>
-    <definedName name="solver_eng" localSheetId="33" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="34" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="14" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="27" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="7" hidden="1">2</definedName>
@@ -157,18 +162,19 @@
     <definedName name="solver_eng" localSheetId="8" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="15" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="17" hidden="1">2</definedName>
-    <definedName name="solver_eng" localSheetId="30" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="31" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="10" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="23" hidden="1">2</definedName>
     <definedName name="solver_est" localSheetId="11" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="20" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="6" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="29" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="30" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="21" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="28" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="22" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="16" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="5" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="33" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="34" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="14" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="27" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="7" hidden="1">1</definedName>
@@ -183,12 +189,13 @@
     <definedName name="solver_itr" localSheetId="11" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="20" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="6" hidden="1">2147483647</definedName>
-    <definedName name="solver_itr" localSheetId="29" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="30" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="21" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="28" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="22" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="16" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="5" hidden="1">2147483647</definedName>
-    <definedName name="solver_itr" localSheetId="33" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="34" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="14" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="27" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="7" hidden="1">2147483647</definedName>
@@ -203,8 +210,9 @@
     <definedName name="solver_lhs1" localSheetId="11" hidden="1">AssignmentProblem!$C$17:$F$17</definedName>
     <definedName name="solver_lhs1" localSheetId="20" hidden="1">CapitalBudget!$B$14</definedName>
     <definedName name="solver_lhs1" localSheetId="6" hidden="1">Dual!$M$6:$M$7</definedName>
-    <definedName name="solver_lhs1" localSheetId="29" hidden="1">EOQ!$J$15</definedName>
+    <definedName name="solver_lhs1" localSheetId="30" hidden="1">EOQ!$J$15</definedName>
     <definedName name="solver_lhs1" localSheetId="21" hidden="1">FixedCost!$B$14:$F$14</definedName>
+    <definedName name="solver_lhs1" localSheetId="28" hidden="1">GameTheory!$B$2:$C$2</definedName>
     <definedName name="solver_lhs1" localSheetId="22" hidden="1">Hub!$B$21:$M$21</definedName>
     <definedName name="solver_lhs1" localSheetId="16" hidden="1">'HW3'!$L$14:$L$17</definedName>
     <definedName name="solver_lhs1" localSheetId="5" hidden="1">LM_2!$J$12:$J$14</definedName>
@@ -232,6 +240,7 @@
     <definedName name="solver_lhs2" localSheetId="11" hidden="1">AssignmentProblem!$G$13:$G$16</definedName>
     <definedName name="solver_lhs2" localSheetId="20" hidden="1">CapitalBudget!$B$10:$H$10</definedName>
     <definedName name="solver_lhs2" localSheetId="21" hidden="1">FixedCost!$B$15:$F$15</definedName>
+    <definedName name="solver_lhs2" localSheetId="28" hidden="1">GameTheory!$E$4:$E$5</definedName>
     <definedName name="solver_lhs2" localSheetId="22" hidden="1">Hub!$B$25:$B$36</definedName>
     <definedName name="solver_lhs2" localSheetId="16" hidden="1">'HW3'!$L$5</definedName>
     <definedName name="solver_lhs2" localSheetId="5" hidden="1">LM_2!$J$15</definedName>
@@ -250,6 +259,7 @@
     <definedName name="solver_lhs22" localSheetId="8" hidden="1">project!$I$11</definedName>
     <definedName name="solver_lhs3" localSheetId="20" hidden="1">CapitalBudget!$C$15</definedName>
     <definedName name="solver_lhs3" localSheetId="21" hidden="1">FixedCost!$B$23:$B$24</definedName>
+    <definedName name="solver_lhs3" localSheetId="28" hidden="1">GameTheory!$E$6</definedName>
     <definedName name="solver_lhs3" localSheetId="16" hidden="1">'HW3'!$E$5:$E$6</definedName>
     <definedName name="solver_lhs3" localSheetId="5" hidden="1">LM_2!$J$15</definedName>
     <definedName name="solver_lhs3" localSheetId="14" hidden="1">MCNF!$L$20:$L$21</definedName>
@@ -261,6 +271,7 @@
     <definedName name="solver_lhs3" localSheetId="15" hidden="1">RedBrandLogistics!$K$20:$K$21</definedName>
     <definedName name="solver_lhs4" localSheetId="20" hidden="1">CapitalBudget!$B$10:$H$10</definedName>
     <definedName name="solver_lhs4" localSheetId="21" hidden="1">FixedCost!$B$23:$B$24</definedName>
+    <definedName name="solver_lhs4" localSheetId="28" hidden="1">GameTheory!$E$6</definedName>
     <definedName name="solver_lhs4" localSheetId="16" hidden="1">'HW3'!$L$9:$L$10</definedName>
     <definedName name="solver_lhs4" localSheetId="14" hidden="1">MCNF!$L$9:$L$11</definedName>
     <definedName name="solver_lhs4" localSheetId="8" hidden="1">project!$I$22</definedName>
@@ -276,12 +287,13 @@
     <definedName name="solver_mip" localSheetId="11" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="20" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="6" hidden="1">2147483647</definedName>
-    <definedName name="solver_mip" localSheetId="29" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="30" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="21" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="28" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="22" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="16" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="5" hidden="1">2147483647</definedName>
-    <definedName name="solver_mip" localSheetId="33" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="34" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="14" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="27" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="7" hidden="1">2147483647</definedName>
@@ -296,12 +308,13 @@
     <definedName name="solver_mni" localSheetId="11" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="20" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="6" hidden="1">30</definedName>
-    <definedName name="solver_mni" localSheetId="29" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="30" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="21" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="28" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="22" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="16" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="5" hidden="1">30</definedName>
-    <definedName name="solver_mni" localSheetId="33" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="34" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="14" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="27" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="7" hidden="1">30</definedName>
@@ -316,12 +329,13 @@
     <definedName name="solver_mrt" localSheetId="11" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="20" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="6" hidden="1">0.075</definedName>
-    <definedName name="solver_mrt" localSheetId="29" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="30" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="21" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="28" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="22" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="16" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="5" hidden="1">0.075</definedName>
-    <definedName name="solver_mrt" localSheetId="33" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="34" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="14" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="27" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="7" hidden="1">0.075</definedName>
@@ -336,12 +350,13 @@
     <definedName name="solver_msl" localSheetId="11" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="20" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="6" hidden="1">2</definedName>
-    <definedName name="solver_msl" localSheetId="29" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="30" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="21" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="28" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="22" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="16" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="5" hidden="1">2</definedName>
-    <definedName name="solver_msl" localSheetId="33" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="34" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="14" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="27" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="7" hidden="1">2</definedName>
@@ -356,12 +371,13 @@
     <definedName name="solver_neg" localSheetId="11" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="20" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="6" hidden="1">1</definedName>
-    <definedName name="solver_neg" localSheetId="29" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="30" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="21" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="28" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="22" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="16" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="5" hidden="1">1</definedName>
-    <definedName name="solver_neg" localSheetId="33" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="34" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="14" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="27" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="7" hidden="1">1</definedName>
@@ -371,18 +387,19 @@
     <definedName name="solver_neg" localSheetId="8" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="15" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="17" hidden="1">1</definedName>
-    <definedName name="solver_neg" localSheetId="30" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="31" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="10" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="23" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="11" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="20" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="6" hidden="1">2147483647</definedName>
-    <definedName name="solver_nod" localSheetId="29" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="30" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="21" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="28" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="22" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="16" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="5" hidden="1">2147483647</definedName>
-    <definedName name="solver_nod" localSheetId="33" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="34" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="14" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="27" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="7" hidden="1">2147483647</definedName>
@@ -397,12 +414,13 @@
     <definedName name="solver_num" localSheetId="11" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="20" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="6" hidden="1">1</definedName>
-    <definedName name="solver_num" localSheetId="29" hidden="1">0</definedName>
+    <definedName name="solver_num" localSheetId="30" hidden="1">0</definedName>
     <definedName name="solver_num" localSheetId="21" hidden="1">3</definedName>
+    <definedName name="solver_num" localSheetId="28" hidden="1">3</definedName>
     <definedName name="solver_num" localSheetId="22" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="16" hidden="1">4</definedName>
     <definedName name="solver_num" localSheetId="5" hidden="1">2</definedName>
-    <definedName name="solver_num" localSheetId="33" hidden="1">0</definedName>
+    <definedName name="solver_num" localSheetId="34" hidden="1">0</definedName>
     <definedName name="solver_num" localSheetId="14" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="27" hidden="1">1</definedName>
     <definedName name="solver_num" localSheetId="7" hidden="1">3</definedName>
@@ -412,18 +430,19 @@
     <definedName name="solver_num" localSheetId="8" hidden="1">22</definedName>
     <definedName name="solver_num" localSheetId="15" hidden="1">4</definedName>
     <definedName name="solver_num" localSheetId="17" hidden="1">2</definedName>
-    <definedName name="solver_num" localSheetId="30" hidden="1">0</definedName>
+    <definedName name="solver_num" localSheetId="31" hidden="1">0</definedName>
     <definedName name="solver_num" localSheetId="10" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="23" hidden="1">2</definedName>
     <definedName name="solver_nwt" localSheetId="11" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="20" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="6" hidden="1">1</definedName>
-    <definedName name="solver_nwt" localSheetId="29" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="30" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="21" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="28" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="22" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="16" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="5" hidden="1">1</definedName>
-    <definedName name="solver_nwt" localSheetId="33" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="34" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="14" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="27" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="7" hidden="1">1</definedName>
@@ -438,12 +457,13 @@
     <definedName name="solver_opt" localSheetId="11" hidden="1">AssignmentProblem!$B$22</definedName>
     <definedName name="solver_opt" localSheetId="20" hidden="1">CapitalBudget!$B$17</definedName>
     <definedName name="solver_opt" localSheetId="6" hidden="1">Dual!$M$5</definedName>
-    <definedName name="solver_opt" localSheetId="29" hidden="1">EOQ!$B$11</definedName>
+    <definedName name="solver_opt" localSheetId="30" hidden="1">EOQ!$B$11</definedName>
     <definedName name="solver_opt" localSheetId="21" hidden="1">FixedCost!$B$30</definedName>
+    <definedName name="solver_opt" localSheetId="28" hidden="1">GameTheory!$E$3</definedName>
     <definedName name="solver_opt" localSheetId="22" hidden="1">Hub!$B$39</definedName>
     <definedName name="solver_opt" localSheetId="16" hidden="1">'HW3'!$B$17</definedName>
     <definedName name="solver_opt" localSheetId="5" hidden="1">LM_2!$K$11</definedName>
-    <definedName name="solver_opt" localSheetId="33" hidden="1">Location!$F$7</definedName>
+    <definedName name="solver_opt" localSheetId="34" hidden="1">Location!$F$7</definedName>
     <definedName name="solver_opt" localSheetId="14" hidden="1">MCNF!$B$17</definedName>
     <definedName name="solver_opt" localSheetId="27" hidden="1">Peakload!$B$26</definedName>
     <definedName name="solver_opt" localSheetId="7" hidden="1">ProdPlanning!$H$28</definedName>
@@ -453,18 +473,19 @@
     <definedName name="solver_opt" localSheetId="8" hidden="1">project!$I$24</definedName>
     <definedName name="solver_opt" localSheetId="15" hidden="1">RedBrandLogistics!$B$36</definedName>
     <definedName name="solver_opt" localSheetId="17" hidden="1">set_covering_model!$C$10</definedName>
-    <definedName name="solver_opt" localSheetId="30" hidden="1">'SVM1'!$F$2</definedName>
+    <definedName name="solver_opt" localSheetId="31" hidden="1">'SVM1'!$F$2</definedName>
     <definedName name="solver_opt" localSheetId="10" hidden="1">Transport1!$B$21</definedName>
     <definedName name="solver_opt" localSheetId="23" hidden="1">WorkerScheduling!$U$4</definedName>
     <definedName name="solver_pre" localSheetId="11" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="20" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="6" hidden="1">0.000001</definedName>
-    <definedName name="solver_pre" localSheetId="29" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="30" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="21" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="28" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="22" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="16" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="5" hidden="1">0.000001</definedName>
-    <definedName name="solver_pre" localSheetId="33" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="34" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="14" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="27" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="7" hidden="1">0.000001</definedName>
@@ -479,12 +500,13 @@
     <definedName name="solver_rbv" localSheetId="11" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="20" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="6" hidden="1">1</definedName>
-    <definedName name="solver_rbv" localSheetId="29" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="30" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="21" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="28" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="22" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="16" hidden="1">2</definedName>
     <definedName name="solver_rbv" localSheetId="5" hidden="1">1</definedName>
-    <definedName name="solver_rbv" localSheetId="33" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="34" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="14" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="27" hidden="1">2</definedName>
     <definedName name="solver_rbv" localSheetId="7" hidden="1">1</definedName>
@@ -499,8 +521,9 @@
     <definedName name="solver_rel1" localSheetId="11" hidden="1">2</definedName>
     <definedName name="solver_rel1" localSheetId="20" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="6" hidden="1">3</definedName>
-    <definedName name="solver_rel1" localSheetId="29" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="30" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="21" hidden="1">5</definedName>
+    <definedName name="solver_rel1" localSheetId="28" hidden="1">3</definedName>
     <definedName name="solver_rel1" localSheetId="22" hidden="1">5</definedName>
     <definedName name="solver_rel1" localSheetId="16" hidden="1">3</definedName>
     <definedName name="solver_rel1" localSheetId="5" hidden="1">2</definedName>
@@ -528,6 +551,7 @@
     <definedName name="solver_rel2" localSheetId="11" hidden="1">2</definedName>
     <definedName name="solver_rel2" localSheetId="20" hidden="1">5</definedName>
     <definedName name="solver_rel2" localSheetId="21" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="28" hidden="1">3</definedName>
     <definedName name="solver_rel2" localSheetId="22" hidden="1">3</definedName>
     <definedName name="solver_rel2" localSheetId="16" hidden="1">2</definedName>
     <definedName name="solver_rel2" localSheetId="5" hidden="1">1</definedName>
@@ -546,6 +570,7 @@
     <definedName name="solver_rel22" localSheetId="8" hidden="1">3</definedName>
     <definedName name="solver_rel3" localSheetId="20" hidden="1">1</definedName>
     <definedName name="solver_rel3" localSheetId="21" hidden="1">1</definedName>
+    <definedName name="solver_rel3" localSheetId="28" hidden="1">2</definedName>
     <definedName name="solver_rel3" localSheetId="16" hidden="1">1</definedName>
     <definedName name="solver_rel3" localSheetId="5" hidden="1">1</definedName>
     <definedName name="solver_rel3" localSheetId="14" hidden="1">3</definedName>
@@ -557,6 +582,7 @@
     <definedName name="solver_rel3" localSheetId="15" hidden="1">3</definedName>
     <definedName name="solver_rel4" localSheetId="20" hidden="1">1</definedName>
     <definedName name="solver_rel4" localSheetId="21" hidden="1">1</definedName>
+    <definedName name="solver_rel4" localSheetId="28" hidden="1">3</definedName>
     <definedName name="solver_rel4" localSheetId="16" hidden="1">2</definedName>
     <definedName name="solver_rel4" localSheetId="14" hidden="1">1</definedName>
     <definedName name="solver_rel4" localSheetId="8" hidden="1">1</definedName>
@@ -570,8 +596,9 @@
     <definedName name="solver_rhs1" localSheetId="11" hidden="1">1</definedName>
     <definedName name="solver_rhs1" localSheetId="20" hidden="1">CapitalBudget!$D$14</definedName>
     <definedName name="solver_rhs1" localSheetId="6" hidden="1">Dual!$O$6:$O$7</definedName>
-    <definedName name="solver_rhs1" localSheetId="29" hidden="1">EOQ!$L$15</definedName>
+    <definedName name="solver_rhs1" localSheetId="30" hidden="1">EOQ!$L$15</definedName>
     <definedName name="solver_rhs1" localSheetId="21" hidden="1">"binary"</definedName>
+    <definedName name="solver_rhs1" localSheetId="28" hidden="1">0</definedName>
     <definedName name="solver_rhs1" localSheetId="22" hidden="1">binary</definedName>
     <definedName name="solver_rhs1" localSheetId="16" hidden="1">'HW3'!$N$14:$N$17</definedName>
     <definedName name="solver_rhs1" localSheetId="5" hidden="1">LM_2!$L$12:$L$14</definedName>
@@ -599,6 +626,7 @@
     <definedName name="solver_rhs2" localSheetId="11" hidden="1">1</definedName>
     <definedName name="solver_rhs2" localSheetId="20" hidden="1">"binary"</definedName>
     <definedName name="solver_rhs2" localSheetId="21" hidden="1">FixedCost!$B$17:$F$17</definedName>
+    <definedName name="solver_rhs2" localSheetId="28" hidden="1">GameTheory!$G$4:$G$5</definedName>
     <definedName name="solver_rhs2" localSheetId="22" hidden="1">Hub!$D$25:$D$36</definedName>
     <definedName name="solver_rhs2" localSheetId="16" hidden="1">'HW3'!$N$5</definedName>
     <definedName name="solver_rhs2" localSheetId="5" hidden="1">LM_2!$L$15</definedName>
@@ -617,6 +645,7 @@
     <definedName name="solver_rhs22" localSheetId="8" hidden="1">EFinish</definedName>
     <definedName name="solver_rhs3" localSheetId="20" hidden="1">0</definedName>
     <definedName name="solver_rhs3" localSheetId="21" hidden="1">FixedCost!$D$23:$D$24</definedName>
+    <definedName name="solver_rhs3" localSheetId="28" hidden="1">1</definedName>
     <definedName name="solver_rhs3" localSheetId="16" hidden="1">'HW3'!$G$5:$G$6</definedName>
     <definedName name="solver_rhs3" localSheetId="5" hidden="1">LM_2!$L$15</definedName>
     <definedName name="solver_rhs3" localSheetId="14" hidden="1">MCNF!$N$20:$N$21</definedName>
@@ -628,6 +657,7 @@
     <definedName name="solver_rhs3" localSheetId="15" hidden="1">RedBrandLogistics!$M$20:$M$21</definedName>
     <definedName name="solver_rhs4" localSheetId="20" hidden="1">1</definedName>
     <definedName name="solver_rhs4" localSheetId="21" hidden="1">FixedCost!$D$23:$D$24</definedName>
+    <definedName name="solver_rhs4" localSheetId="28" hidden="1">1</definedName>
     <definedName name="solver_rhs4" localSheetId="16" hidden="1">'HW3'!$N$9:$N$10</definedName>
     <definedName name="solver_rhs4" localSheetId="14" hidden="1">MCNF!$N$9:$N$11</definedName>
     <definedName name="solver_rhs4" localSheetId="8" hidden="1">project!$K$22</definedName>
@@ -641,12 +671,13 @@
     <definedName name="solver_rlx" localSheetId="11" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="20" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="6" hidden="1">2</definedName>
-    <definedName name="solver_rlx" localSheetId="29" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="30" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="21" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="28" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="22" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="16" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="5" hidden="1">2</definedName>
-    <definedName name="solver_rlx" localSheetId="33" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="34" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="14" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="27" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="7" hidden="1">2</definedName>
@@ -661,12 +692,13 @@
     <definedName name="solver_rsd" localSheetId="11" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="20" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="6" hidden="1">0</definedName>
-    <definedName name="solver_rsd" localSheetId="29" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="30" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="21" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="28" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="22" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="16" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="5" hidden="1">0</definedName>
-    <definedName name="solver_rsd" localSheetId="33" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="34" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="14" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="27" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="7" hidden="1">0</definedName>
@@ -681,12 +713,13 @@
     <definedName name="solver_scl" localSheetId="11" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="20" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="6" hidden="1">1</definedName>
-    <definedName name="solver_scl" localSheetId="29" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="30" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="21" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="28" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="22" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="16" hidden="1">2</definedName>
     <definedName name="solver_scl" localSheetId="5" hidden="1">1</definedName>
-    <definedName name="solver_scl" localSheetId="33" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="34" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="14" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="27" hidden="1">2</definedName>
     <definedName name="solver_scl" localSheetId="7" hidden="1">1</definedName>
@@ -701,12 +734,13 @@
     <definedName name="solver_sho" localSheetId="11" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="20" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="6" hidden="1">2</definedName>
-    <definedName name="solver_sho" localSheetId="29" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="30" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="21" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="28" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="22" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="16" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="5" hidden="1">2</definedName>
-    <definedName name="solver_sho" localSheetId="33" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="34" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="14" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="27" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="7" hidden="1">2</definedName>
@@ -721,12 +755,13 @@
     <definedName name="solver_ssz" localSheetId="11" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="20" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="6" hidden="1">100</definedName>
-    <definedName name="solver_ssz" localSheetId="29" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="30" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="21" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="28" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="22" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="16" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="5" hidden="1">100</definedName>
-    <definedName name="solver_ssz" localSheetId="33" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="34" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="14" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="27" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="7" hidden="1">100</definedName>
@@ -741,12 +776,13 @@
     <definedName name="solver_tim" localSheetId="11" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="20" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="6" hidden="1">2147483647</definedName>
-    <definedName name="solver_tim" localSheetId="29" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="30" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="21" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="28" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="22" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="16" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="5" hidden="1">2147483647</definedName>
-    <definedName name="solver_tim" localSheetId="33" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="34" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="14" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="27" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="7" hidden="1">2147483647</definedName>
@@ -761,12 +797,13 @@
     <definedName name="solver_tol" localSheetId="11" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="20" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="6" hidden="1">0.01</definedName>
-    <definedName name="solver_tol" localSheetId="29" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="30" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="21" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="28" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="22" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="16" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="5" hidden="1">0.01</definedName>
-    <definedName name="solver_tol" localSheetId="33" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="34" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="14" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="27" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="7" hidden="1">0.01</definedName>
@@ -781,12 +818,13 @@
     <definedName name="solver_typ" localSheetId="11" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="20" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="6" hidden="1">2</definedName>
-    <definedName name="solver_typ" localSheetId="29" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="30" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="21" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="28" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="22" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="16" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="5" hidden="1">2</definedName>
-    <definedName name="solver_typ" localSheetId="33" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="34" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="14" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="27" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="7" hidden="1">2</definedName>
@@ -796,18 +834,19 @@
     <definedName name="solver_typ" localSheetId="8" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="15" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="17" hidden="1">2</definedName>
-    <definedName name="solver_typ" localSheetId="30" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="31" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="10" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="23" hidden="1">2</definedName>
     <definedName name="solver_val" localSheetId="11" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="20" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="6" hidden="1">0</definedName>
-    <definedName name="solver_val" localSheetId="29" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="30" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="21" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="28" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="22" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="16" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="5" hidden="1">0</definedName>
-    <definedName name="solver_val" localSheetId="33" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="34" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="14" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="27" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="7" hidden="1">0</definedName>
@@ -817,18 +856,19 @@
     <definedName name="solver_val" localSheetId="8" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="15" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="17" hidden="1">0</definedName>
-    <definedName name="solver_val" localSheetId="30" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="31" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="10" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="23" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="11" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="20" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="6" hidden="1">3</definedName>
-    <definedName name="solver_ver" localSheetId="29" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="30" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="21" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="28" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="22" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="16" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="5" hidden="1">3</definedName>
-    <definedName name="solver_ver" localSheetId="33" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="34" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="14" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="27" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="7" hidden="1">3</definedName>
@@ -838,7 +878,7 @@
     <definedName name="solver_ver" localSheetId="8" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="15" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="17" hidden="1">3</definedName>
-    <definedName name="solver_ver" localSheetId="30" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="31" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="10" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="23" hidden="1">3</definedName>
     <definedName name="yFinish">project!$I$22</definedName>
@@ -949,7 +989,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="606">
   <si>
     <t>Assembling and testing computers</t>
   </si>
@@ -3034,6 +3074,21 @@
   </si>
   <si>
     <t>*ถ้า ไป-กลับ ก็เอา distance คูณสอง</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>Obj</t>
+  </si>
+  <si>
+    <t>Con1</t>
+  </si>
+  <si>
+    <t>Con2</t>
+  </si>
+  <si>
+    <t>Con3</t>
   </si>
 </sst>
 </file>
@@ -3576,7 +3631,7 @@
     <xf numFmtId="192" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3777,9 +3832,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3787,6 +3839,10 @@
     <xf numFmtId="190" fontId="4" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="189" fontId="4" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Comma" xfId="6" builtinId="3"/>
@@ -19632,10 +19688,10 @@
       <c r="A13" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="B13" s="131">
+      <c r="B13" s="130">
         <v>137.57112194445477</v>
       </c>
-      <c r="C13" s="131">
+      <c r="C13" s="130">
         <v>75.848899722255098</v>
       </c>
     </row>
@@ -19648,7 +19704,7 @@
       <c r="A15" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="B15" s="132">
+      <c r="B15" s="131">
         <v>0.69212211388844735</v>
       </c>
       <c r="C15" s="70"/>
@@ -19737,7 +19793,7 @@
       <c r="A26" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="B26" s="133">
+      <c r="B26" s="132">
         <f>B24-B25</f>
         <v>95.803558000503784</v>
       </c>
@@ -19751,6 +19807,406 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E329189-507B-492C-B892-EA89AEC44AA6}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="B1" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B2" s="52">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="C2" s="52">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="D2" s="52">
+        <v>-4.3636363636363633</v>
+      </c>
+      <c r="E2" s="134"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>602</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="101">
+        <f t="shared" ref="E3:E5" si="0">SUMPRODUCT(B3:D3,$B$2:$D$2)</f>
+        <v>-4.3636363636363633</v>
+      </c>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>603</v>
+      </c>
+      <c r="B4">
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>-8</v>
+      </c>
+      <c r="D4">
+        <v>-1</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>604</v>
+      </c>
+      <c r="B5">
+        <v>-6</v>
+      </c>
+      <c r="C5">
+        <v>-4</v>
+      </c>
+      <c r="D5">
+        <v>-1</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>605</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <f>SUMPRODUCT(B6:D6,$B$2:$D$2)</f>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="11" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F03746BD-BE34-41ED-A93B-E2B7AB36F190}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="47.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.6875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.6875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="B7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3">
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5">
+        <v>150</v>
+      </c>
+      <c r="C10" s="5">
+        <v>225</v>
+      </c>
+      <c r="D10">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5">
+        <v>300</v>
+      </c>
+      <c r="C11" s="5">
+        <v>450</v>
+      </c>
+      <c r="D11">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="6">
+        <f>B11-(B10+SUMPRODUCT($B$3:$B$4,B8:B9))</f>
+        <v>80</v>
+      </c>
+      <c r="C12" s="6">
+        <f t="shared" ref="C12" si="0">C11-(C10+SUMPRODUCT($B$3:$B$4,C8:C9))</f>
+        <v>129</v>
+      </c>
+      <c r="D12" s="6">
+        <f>D11-(D10+SUMPRODUCT($B$3:$B$4,D8:D9))</f>
+        <v>152</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="B15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="4">
+        <v>514.28571428571433</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D16" s="2">
+        <v>28.571428571428569</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="B17" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3">
+        <v>600</v>
+      </c>
+      <c r="C18" s="3">
+        <v>1200</v>
+      </c>
+      <c r="D18" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21">
+        <f>SUMPRODUCT(B16:D16,B8:D8)</f>
+        <v>10000.000000000002</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="D21" s="3">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22">
+        <f>SUMPRODUCT(B16:D16,B9:D9)</f>
+        <v>3000</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="D22" s="3">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="B25" s="6">
+        <f>B12*B16</f>
+        <v>41142.857142857145</v>
+      </c>
+      <c r="C25" s="6">
+        <f>C12*C16</f>
+        <v>154800</v>
+      </c>
+      <c r="D25" s="7">
+        <f>SUM(B25:C25)</f>
+        <v>195942.85714285716</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="D26">
+        <f>SUMPRODUCT(B12:D12,B16:D16)</f>
+        <v>200285.71428571429</v>
+      </c>
+      <c r="E26" t="s">
+        <v>474</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="1" gridLines="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:I28"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -20312,278 +20768,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F03746BD-BE34-41ED-A93B-E2B7AB36F190}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="47.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.6875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="2.125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.6875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="B7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="3">
-        <v>5</v>
-      </c>
-      <c r="C8" s="3">
-        <v>6</v>
-      </c>
-      <c r="D8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="3">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3">
-        <v>2</v>
-      </c>
-      <c r="D9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="5">
-        <v>150</v>
-      </c>
-      <c r="C10" s="5">
-        <v>225</v>
-      </c>
-      <c r="D10">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="5">
-        <v>300</v>
-      </c>
-      <c r="C11" s="5">
-        <v>450</v>
-      </c>
-      <c r="D11">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="6">
-        <f>B11-(B10+SUMPRODUCT($B$3:$B$4,B8:B9))</f>
-        <v>80</v>
-      </c>
-      <c r="C12" s="6">
-        <f t="shared" ref="C12" si="0">C11-(C10+SUMPRODUCT($B$3:$B$4,C8:C9))</f>
-        <v>129</v>
-      </c>
-      <c r="D12" s="6">
-        <f>D11-(D10+SUMPRODUCT($B$3:$B$4,D8:D9))</f>
-        <v>152</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="B15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="4">
-        <v>514.28571428571433</v>
-      </c>
-      <c r="C16" s="4">
-        <v>1200</v>
-      </c>
-      <c r="D16" s="2">
-        <v>28.571428571428569</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="B17" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="3">
-        <v>600</v>
-      </c>
-      <c r="C18" s="3">
-        <v>1200</v>
-      </c>
-      <c r="D18" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21">
-        <f>SUMPRODUCT(B16:D16,B8:D8)</f>
-        <v>10000.000000000002</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="D21" s="3">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22">
-        <f>SUMPRODUCT(B16:D16,B9:D9)</f>
-        <v>3000</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="D22" s="3">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="B25" s="6">
-        <f>B12*B16</f>
-        <v>41142.857142857145</v>
-      </c>
-      <c r="C25" s="6">
-        <f>C12*C16</f>
-        <v>154800</v>
-      </c>
-      <c r="D25" s="7">
-        <f>SUM(B25:C25)</f>
-        <v>195942.85714285716</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="D26">
-        <f>SUMPRODUCT(B12:D12,B16:D16)</f>
-        <v>200285.71428571429</v>
-      </c>
-      <c r="E26" t="s">
-        <v>474</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="1" gridLines="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EAD1EC8-752F-43D6-B790-5A15DDCDB8C8}">
   <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -20657,8 +20842,8 @@
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="129"/>
-      <c r="B5" s="129"/>
+      <c r="A5" s="128"/>
+      <c r="B5" s="128"/>
       <c r="F5" t="s">
         <v>370</v>
       </c>
@@ -20693,7 +20878,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="27">
-      <c r="A7" s="130" t="s">
+      <c r="A7" s="129" t="s">
         <v>598</v>
       </c>
       <c r="B7">
@@ -20705,7 +20890,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="27">
-      <c r="A8" s="130" t="s">
+      <c r="A8" s="129" t="s">
         <v>599</v>
       </c>
       <c r="B8">
@@ -20726,7 +20911,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="27">
-      <c r="A9" s="130" t="s">
+      <c r="A9" s="129" t="s">
         <v>597</v>
       </c>
       <c r="B9">
@@ -20788,7 +20973,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60333241-7CED-4A17-BDC1-56C6BD21859E}">
   <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -21168,7 +21353,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63314198-B56A-4E6A-9111-45ED4BF145FD}">
   <dimension ref="A2:J21"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -21487,7 +21672,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FC3221A-5E02-4AAB-87CE-F72249FF67DB}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -21621,7 +21806,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46A71A95-F527-448F-A238-508D8B187D7B}">
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -21757,13 +21942,13 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="128" t="s">
+      <c r="A7" s="133" t="s">
         <v>441</v>
       </c>
-      <c r="B7" s="128"/>
-      <c r="C7" s="128"/>
-      <c r="D7" s="128"/>
-      <c r="E7" s="128"/>
+      <c r="B7" s="133"/>
+      <c r="C7" s="133"/>
+      <c r="D7" s="133"/>
+      <c r="E7" s="133"/>
       <c r="F7" s="91">
         <f>SUMPRODUCT(F2:F5,E2:E5)</f>
         <v>5456.5396875145925</v>
@@ -25295,21 +25480,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005D21A9346877C94FBE0D2EF98A54C8DF" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="751dbf132c53fd3bc3488d6191458457">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="500c6692915ba10984c0aabd49f31b22">
     <xsd:element name="properties">
@@ -25423,10 +25593,32 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE94C634-99D9-44FC-B2A2-D1462FE9BD9E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{633191C1-D2B6-4B97-A701-AFB02492B9AF}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
@@ -25441,16 +25633,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{633191C1-D2B6-4B97-A701-AFB02492B9AF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE94C634-99D9-44FC-B2A2-D1462FE9BD9E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
